--- a/外務當日派件紀錄表.xlsx
+++ b/外務當日派件紀錄表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\優化表單\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14794FDD-7DEA-468C-A474-14B35C5685ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D152171E-4A3E-479D-9886-117ABE7B4306}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6840" xr2:uid="{340182F3-18AA-44C0-BA70-CD503619309B}"/>
   </bookViews>
@@ -224,7 +224,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -358,36 +358,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -461,10 +431,10 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -851,7 +821,7 @@
     </row>
     <row r="4" spans="1:10" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
-      <c r="B4" s="11"/>
+      <c r="B4" s="2"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -865,8 +835,8 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="1"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="14"/>
       <c r="E5" s="13"/>
       <c r="F5" s="6"/>
@@ -876,8 +846,8 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="14"/>
       <c r="E6" s="13"/>
       <c r="F6" s="6"/>
@@ -887,8 +857,8 @@
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="22"/>
       <c r="D7" s="14"/>
       <c r="E7" s="13"/>
       <c r="F7" s="6"/>
@@ -898,8 +868,8 @@
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="1"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="14"/>
       <c r="E8" s="13"/>
       <c r="F8" s="6"/>
@@ -909,8 +879,8 @@
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="1"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="14"/>
       <c r="E9" s="13"/>
       <c r="F9" s="6"/>
@@ -920,8 +890,8 @@
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="14"/>
       <c r="E10" s="13"/>
       <c r="F10" s="6"/>
@@ -931,8 +901,8 @@
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="1"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="14"/>
       <c r="E11" s="13"/>
       <c r="F11" s="6"/>
@@ -942,8 +912,8 @@
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="1"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="14"/>
       <c r="E12" s="13"/>
       <c r="F12" s="6"/>
@@ -953,8 +923,8 @@
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="1"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="14"/>
       <c r="E13" s="13"/>
       <c r="F13" s="6"/>
@@ -964,8 +934,8 @@
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="1"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="14"/>
       <c r="E14" s="13"/>
       <c r="F14" s="6"/>
@@ -975,8 +945,8 @@
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="1"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="14"/>
       <c r="E15" s="13"/>
       <c r="F15" s="6"/>
@@ -986,8 +956,8 @@
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="1"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="22"/>
       <c r="D16" s="14"/>
       <c r="E16" s="13"/>
       <c r="F16" s="6"/>
@@ -997,8 +967,8 @@
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="1"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="14"/>
       <c r="E17" s="13"/>
       <c r="F17" s="6"/>
@@ -1008,8 +978,8 @@
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="1"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="22"/>
       <c r="D18" s="14"/>
       <c r="E18" s="13"/>
       <c r="F18" s="6"/>
@@ -1019,8 +989,8 @@
       <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="1"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="14"/>
       <c r="E19" s="13"/>
       <c r="F19" s="6"/>
@@ -1030,8 +1000,8 @@
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="1"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="22"/>
       <c r="D20" s="14"/>
       <c r="E20" s="13"/>
       <c r="F20" s="6"/>
@@ -1041,8 +1011,8 @@
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="1"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="22"/>
       <c r="D21" s="14"/>
       <c r="E21" s="13"/>
       <c r="F21" s="6"/>
@@ -1052,8 +1022,8 @@
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="1"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="22"/>
       <c r="D22" s="14"/>
       <c r="E22" s="13"/>
       <c r="F22" s="6"/>
@@ -1063,8 +1033,8 @@
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="1"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="22"/>
       <c r="D23" s="14"/>
       <c r="E23" s="13"/>
       <c r="F23" s="6"/>
@@ -1074,8 +1044,8 @@
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="1"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="22"/>
       <c r="D24" s="14"/>
       <c r="E24" s="13"/>
       <c r="F24" s="6"/>
@@ -1085,8 +1055,8 @@
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="1"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="22"/>
       <c r="D25" s="14"/>
       <c r="E25" s="13"/>
       <c r="F25" s="6"/>
@@ -1096,8 +1066,8 @@
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="1"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="22"/>
       <c r="D26" s="14"/>
       <c r="E26" s="13"/>
       <c r="F26" s="6"/>
@@ -1107,8 +1077,8 @@
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="22"/>
       <c r="D27" s="14"/>
       <c r="E27" s="13"/>
       <c r="F27" s="6"/>

--- a/外務當日派件紀錄表.xlsx
+++ b/外務當日派件紀錄表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\優化表單\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D152171E-4A3E-479D-9886-117ABE7B4306}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99F0F18-5AF7-4FD6-960B-C5188EF78145}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6840" xr2:uid="{340182F3-18AA-44C0-BA70-CD503619309B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">工作表1!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">工作表1!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>已派</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -56,9 +56,6 @@
   <si>
     <t>張振發</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>郭香蘭</t>
   </si>
   <si>
     <t>陳育賓</t>
@@ -131,22 +128,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>洪森賢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉彥璋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>施啓文</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>張春文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>問題件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -161,6 +146,10 @@
   <si>
     <t>年           月           日</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郭香蘭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -419,6 +408,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -429,12 +424,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -751,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D3112A-AB3D-4901-908B-73D6C3CB8710}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="19.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" style="3" customWidth="1"/>
@@ -762,7 +751,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -770,50 +759,50 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
       <c r="G1" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="18"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -833,256 +822,223 @@
     </row>
     <row r="5" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="22"/>
+        <v>17</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="18"/>
       <c r="D5" s="14"/>
       <c r="E5" s="13"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="23"/>
+      <c r="G5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="22"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="14"/>
       <c r="E6" s="13"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="23"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="22"/>
+        <v>7</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="14"/>
       <c r="E7" s="13"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="23"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="22"/>
+        <v>13</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="14"/>
       <c r="E8" s="13"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="23"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="22"/>
+        <v>16</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="14"/>
       <c r="E9" s="13"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="23"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="22"/>
+        <v>18</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="14"/>
       <c r="E10" s="13"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="23"/>
+      <c r="G10" s="19"/>
     </row>
     <row r="11" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="22"/>
+        <v>6</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="14"/>
       <c r="E11" s="13"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="23"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="22"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="14"/>
       <c r="E12" s="13"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="22"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="14"/>
       <c r="E13" s="13"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="22"/>
+        <v>19</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="14"/>
       <c r="E14" s="13"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="23"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="22"/>
+        <v>30</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="14"/>
       <c r="E15" s="13"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="23"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="22"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="14"/>
       <c r="E16" s="13"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="23"/>
+      <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="22"/>
+        <v>20</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="14"/>
       <c r="E17" s="13"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="23"/>
+      <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="22"/>
+        <v>8</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="14"/>
       <c r="E18" s="13"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="23"/>
+      <c r="G18" s="19"/>
     </row>
     <row r="19" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="14"/>
       <c r="E19" s="13"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="23"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="22"/>
+        <v>11</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="14"/>
       <c r="E20" s="13"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="23"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="22"/>
+        <v>12</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="14"/>
       <c r="E21" s="13"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="23"/>
+      <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="22"/>
+        <v>4</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="14"/>
       <c r="E22" s="13"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="23"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="22"/>
+        <v>3</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="14"/>
       <c r="E23" s="13"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="23"/>
+      <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="22"/>
+        <v>25</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="14"/>
       <c r="E24" s="13"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="25" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="23"/>
-    </row>
-    <row r="26" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="27" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="23"/>
+      <c r="G24" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1093,8 +1049,5 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.23622047244094491" top="0.39370078740157483" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="110" fitToWidth="0" orientation="portrait" r:id="rId1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="27" max="8" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>
--- a/外務當日派件紀錄表.xlsx
+++ b/外務當日派件紀錄表.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99F0F18-5AF7-4FD6-960B-C5188EF78145}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02323C31-5F8C-4BFF-972E-378FDEA3D646}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6840" xr2:uid="{340182F3-18AA-44C0-BA70-CD503619309B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17340" windowHeight="8808" xr2:uid="{340182F3-18AA-44C0-BA70-CD503619309B}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">工作表1!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">工作表1!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -822,7 +822,7 @@
     </row>
     <row r="5" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="18"/>
@@ -833,7 +833,7 @@
     </row>
     <row r="6" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="18"/>
@@ -844,7 +844,7 @@
     </row>
     <row r="7" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="18"/>
@@ -855,7 +855,7 @@
     </row>
     <row r="8" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="18"/>
@@ -866,7 +866,7 @@
     </row>
     <row r="9" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="18"/>
@@ -877,7 +877,7 @@
     </row>
     <row r="10" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="18"/>
@@ -886,9 +886,9 @@
       <c r="F10" s="6"/>
       <c r="G10" s="19"/>
     </row>
-    <row r="11" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="18"/>
@@ -899,7 +899,7 @@
     </row>
     <row r="12" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="18"/>
@@ -908,9 +908,9 @@
       <c r="F12" s="6"/>
       <c r="G12" s="19"/>
     </row>
-    <row r="13" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="18"/>
@@ -921,7 +921,7 @@
     </row>
     <row r="14" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="18"/>
@@ -932,7 +932,7 @@
     </row>
     <row r="15" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="18"/>
@@ -943,7 +943,7 @@
     </row>
     <row r="16" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="18"/>
@@ -954,7 +954,7 @@
     </row>
     <row r="17" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="18"/>
@@ -965,7 +965,7 @@
     </row>
     <row r="18" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="18"/>
@@ -976,7 +976,7 @@
     </row>
     <row r="19" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="18"/>
@@ -987,7 +987,7 @@
     </row>
     <row r="20" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="18"/>
@@ -998,7 +998,7 @@
     </row>
     <row r="21" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="18"/>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="22" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="18"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="23" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="18"/>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="24" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="18"/>
